--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.66275937823179</v>
+        <v>9.695198398962667</v>
       </c>
       <c r="D2" t="n">
-        <v>56.98891219352094</v>
+        <v>9.260698231447153</v>
       </c>
       <c r="E2" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F2" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.71738005918278</v>
+        <v>8.729074259617201</v>
       </c>
       <c r="D3" t="n">
-        <v>51.05091706235981</v>
+        <v>8.29577402263347</v>
       </c>
       <c r="E3" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F3" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.06356327982115</v>
+        <v>7.485329032970937</v>
       </c>
       <c r="D4" t="n">
-        <v>43.43378941649978</v>
+        <v>7.057990780181214</v>
       </c>
       <c r="E4" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F4" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.77658274054588</v>
+        <v>4.513694695338706</v>
       </c>
       <c r="D5" t="n">
-        <v>25.97986968894804</v>
+        <v>4.221728824454056</v>
       </c>
       <c r="E5" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F5" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.69073157070375</v>
+        <v>4.012243880239359</v>
       </c>
       <c r="D6" t="n">
-        <v>22.06568569164401</v>
+        <v>3.585673924892152</v>
       </c>
       <c r="E6" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F6" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.11699581864941</v>
+        <v>5.381511820530529</v>
       </c>
       <c r="D7" t="n">
-        <v>34.45873716593019</v>
+        <v>5.599544789463656</v>
       </c>
       <c r="E7" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F7" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.6550767742086</v>
+        <v>4.981449975808898</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95511098288091</v>
+        <v>5.030205534718148</v>
       </c>
       <c r="E8" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F8" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.54423101095836</v>
+        <v>6.100937539280734</v>
       </c>
       <c r="D9" t="n">
-        <v>37.12970738863981</v>
+        <v>6.033577450653969</v>
       </c>
       <c r="E9" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F9" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.47057018092406</v>
+        <v>6.41396765440016</v>
       </c>
       <c r="D10" t="n">
-        <v>39.92267670422869</v>
+        <v>6.487434964437162</v>
       </c>
       <c r="E10" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F10" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.29284882434152</v>
+        <v>6.385087933955497</v>
       </c>
       <c r="D11" t="n">
-        <v>39.46791647544059</v>
+        <v>6.413536427259096</v>
       </c>
       <c r="E11" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F11" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.17661440561393</v>
+        <v>4.416199840912264</v>
       </c>
       <c r="D12" t="n">
-        <v>28.77465803935376</v>
+        <v>4.675881931394986</v>
       </c>
       <c r="E12" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F12" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.50267803146556</v>
+        <v>4.956685180113153</v>
       </c>
       <c r="D13" t="n">
-        <v>31.33094234949585</v>
+        <v>5.091278131793076</v>
       </c>
       <c r="E13" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F13" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.81218155255971</v>
+        <v>5.494479502290954</v>
       </c>
       <c r="D14" t="n">
-        <v>35.6760248258374</v>
+        <v>5.797354034198578</v>
       </c>
       <c r="E14" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F14" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.72590466842603</v>
+        <v>6.13045950861923</v>
       </c>
       <c r="D15" t="n">
-        <v>40.39366470995633</v>
+        <v>6.563970515367904</v>
       </c>
       <c r="E15" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F15" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>6.438699027905585</v>
+        <v>1.046288592034658</v>
       </c>
       <c r="D16" t="n">
-        <v>6.407176080247315</v>
+        <v>1.041166113040189</v>
       </c>
       <c r="E16" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F16" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.59437065429853</v>
+        <v>3.021585231323512</v>
       </c>
       <c r="D17" t="n">
-        <v>18.50771441959446</v>
+        <v>3.0075035931841</v>
       </c>
       <c r="E17" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F17" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>11.96002954963382</v>
+        <v>1.943504801815496</v>
       </c>
       <c r="D18" t="n">
-        <v>11.81173690890782</v>
+        <v>1.91940724769752</v>
       </c>
       <c r="E18" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F18" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>58.33892431852112</v>
+        <v>9.480075201759682</v>
       </c>
       <c r="D19" t="n">
-        <v>61.01029624528282</v>
+        <v>9.914173139858459</v>
       </c>
       <c r="E19" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F19" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>70.34043106267714</v>
+        <v>11.43032004768504</v>
       </c>
       <c r="D20" t="n">
-        <v>70.26088887387041</v>
+        <v>11.41739444200394</v>
       </c>
       <c r="E20" t="n">
-        <v>15.86327120816134</v>
+        <v>2.577781571326217</v>
       </c>
       <c r="F20" t="n">
-        <v>15.7827301239597</v>
+        <v>2.564693645143451</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
